--- a/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,6</t>
+          <t>-4,39; 1,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 8,64</t>
+          <t>-0,76; 8,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 2,74</t>
+          <t>-8,65; 3,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 6,05</t>
+          <t>-1,71; 5,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,58</t>
+          <t>-86,86; 163,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,44; 1169,16</t>
+          <t>-79,22; 1499,51</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 5,8</t>
+          <t>-3,9; 5,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,9</t>
+          <t>-1,99; 4,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 6,58</t>
+          <t>-2,03; 7,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 3,12</t>
+          <t>-6,22; 4,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,34; 540,83</t>
+          <t>-84,83; 506,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,83; 944,05</t>
+          <t>-69,0; 14957201,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,23; 129,96</t>
+          <t>-82,91; 219,9</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; -0,81</t>
+          <t>-7,38; -0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 9,85</t>
+          <t>0,0; 8,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,74</t>
+          <t>-3,06; 7,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 11,98</t>
+          <t>-6,19; 12,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 563,15</t>
+          <t>-71,45; 493,29</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,69</t>
+          <t>-1,12; 4,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,59</t>
+          <t>-0,83; 3,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 3,13</t>
+          <t>-4,34; 2,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 1,1</t>
+          <t>-5,41; 0,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 1044,47</t>
+          <t>-64,91; 939,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,66; 118,17</t>
+          <t>-64,63; 108,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,99; 38,8</t>
+          <t>-75,78; 36,06</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,62; -0,86</t>
+          <t>-9,5; -0,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,3</t>
+          <t>-2,04; 6,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 6,72</t>
+          <t>-5,17; 6,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 5,23</t>
+          <t>-5,64; 5,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 144,93</t>
+          <t>-100,0; 26,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-81,72; —</t>
+          <t>-76,13; 1058,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 184,64</t>
+          <t>-63,38; 161,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 105,51</t>
+          <t>-53,75; 97,84</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,98</t>
+          <t>-3,71; 5,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,87</t>
+          <t>-4,24; 5,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 8,86</t>
+          <t>-6,36; 8,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 7,96</t>
+          <t>-9,28; 7,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,12; 328,39</t>
+          <t>-71,69; 290,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,45; 159,1</t>
+          <t>-67,69; 179,7</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,97</t>
+          <t>-1,93; 0,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,12</t>
+          <t>0,22; 3,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,25</t>
+          <t>-1,76; 2,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,81</t>
+          <t>-2,62; 1,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-57,03; 49,88</t>
+          <t>-57,73; 51,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 357,94</t>
+          <t>6,34; 389,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 60,53</t>
+          <t>-31,3; 62,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-37,44; 39,99</t>
+          <t>-38,89; 38,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,68</t>
+          <t>-3,69; 1,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 8,52</t>
+          <t>-0,79; 8,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 3,67</t>
+          <t>-8,41; 3,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 5,91</t>
+          <t>-1,8; 6,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-86,86; 163,87</t>
+          <t>-88,06; 228,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-79,22; 1499,51</t>
+          <t>-70,36; 1000,05</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 5,59</t>
+          <t>-3,79; 5,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,82</t>
+          <t>-2,0; 4,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 7,74</t>
+          <t>-2,25; 7,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 4,37</t>
+          <t>-5,88; 4,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,83; 506,62</t>
+          <t>-86,41; 470,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-69,0; 14957201,55</t>
+          <t>-74,66; 34134264,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,91; 219,9</t>
+          <t>-80,6; 214,89</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; -0,81</t>
+          <t>-7,67; -0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,86</t>
+          <t>0,0; 9,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,19</t>
+          <t>-3,1; 7,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 12,07</t>
+          <t>-5,79; 12,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,45; 493,29</t>
+          <t>-64,63; 553,59</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,14</t>
+          <t>-1,28; 4,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,84</t>
+          <t>-1,15; 3,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 2,98</t>
+          <t>-4,26; 3,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 0,98</t>
+          <t>-5,56; 0,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 939,66</t>
+          <t>-71,79; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,63; 108,91</t>
+          <t>-62,82; 116,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,78; 36,06</t>
+          <t>-74,0; 36,11</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,5; -0,68</t>
+          <t>-9,84; -1,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 6,2</t>
+          <t>-2,4; 6,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 6,29</t>
+          <t>-5,54; 6,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 5,14</t>
+          <t>-6,1; 5,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,4</t>
+          <t>-100,0; 47,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-76,13; 1058,25</t>
+          <t>-76,79; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,38; 161,91</t>
+          <t>-57,9; 174,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,75; 97,84</t>
+          <t>-55,64; 94,9</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,01</t>
+          <t>-3,8; 5,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 5,7</t>
+          <t>-3,99; 5,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 8,71</t>
+          <t>-5,61; 8,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 7,93</t>
+          <t>-10,24; 7,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>-86,1; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,69; 290,61</t>
+          <t>-67,38; 381,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-67,69; 179,7</t>
+          <t>-70,05; 160,5</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,91</t>
+          <t>-2,06; 1,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,37</t>
+          <t>0,23; 3,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,36</t>
+          <t>-1,75; 2,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,78</t>
+          <t>-2,54; 1,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-57,73; 51,29</t>
+          <t>-60,17; 51,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,34; 389,92</t>
+          <t>5,82; 398,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 62,15</t>
+          <t>-30,07; 72,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 38,67</t>
+          <t>-38,0; 37,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>112,5%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,69</t>
+          <t>-4,43; 1,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 8,41</t>
+          <t>-0,75; 8,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 3,85</t>
+          <t>-9,66; 2,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 6,16</t>
+          <t>-1,8; 6,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-88,06; 228,35</t>
+          <t>-100,0; 121,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-70,36; 1000,05</t>
+          <t>-80,79; 1274,08</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-1,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-23,75%</t>
+          <t>-21,46%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 5,56</t>
+          <t>-4,2; 5,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,86</t>
+          <t>-2,01; 3,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 7,88</t>
+          <t>-2,17; 6,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 4,01</t>
+          <t>-6,59; 3,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,41; 470,42</t>
+          <t>-88,34; 540,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,66; 34134264,83</t>
+          <t>-72,83; 944,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,6; 214,89</t>
+          <t>-83,06; 146,76</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,05</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>57,91%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; -0,81</t>
+          <t>-8,2; -0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>-0,62; 9,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 7,72</t>
+          <t>-3,06; 7,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 12,11</t>
+          <t>-5,05; 13,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-64,63; 553,59</t>
+          <t>-59,95; 614,72</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,14</t>
+          <t>-1,91</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-40,53%</t>
+          <t>-34,23%</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,5</t>
+          <t>-0,94; 4,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,67</t>
+          <t>-0,97; 3,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 3,12</t>
+          <t>-3,96; 3,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 0,98</t>
+          <t>-5,53; 1,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,79; —</t>
+          <t>-59,1; 1044,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,82; 116,41</t>
+          <t>-61,66; 118,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 36,11</t>
+          <t>-72,58; 58,3</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,0%</t>
+          <t>-5,57%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -1,08</t>
+          <t>-9,62; -0,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 6,05</t>
+          <t>-2,29; 6,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 6,24</t>
+          <t>-4,77; 6,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 5,58</t>
+          <t>-5,66; 5,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,05</t>
+          <t>-100,0; 144,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-76,79; —</t>
+          <t>-81,72; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-57,9; 174,11</t>
+          <t>-58,14; 184,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-55,64; 94,9</t>
+          <t>-54,14; 107,7</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-2,45%</t>
+          <t>-8,53%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 5,0</t>
+          <t>-3,82; 4,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,49</t>
+          <t>-3,61; 5,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 8,66</t>
+          <t>-6,06; 8,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 7,5</t>
+          <t>-10,57; 7,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,1; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-67,38; 381,29</t>
+          <t>-69,12; 328,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,05; 160,5</t>
+          <t>-70,78; 160,01</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-7,1%</t>
+          <t>-3,38%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,01</t>
+          <t>-2,03; 0,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,3</t>
+          <t>0,1; 3,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,62</t>
+          <t>-1,88; 2,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,68</t>
+          <t>-2,51; 2,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 51,66</t>
+          <t>-57,03; 49,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 398,7</t>
+          <t>-8,33; 357,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 72,85</t>
+          <t>-32,44; 60,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,0; 37,28</t>
+          <t>-35,12; 47,13</t>
         </is>
       </c>
     </row>
